--- a/LibraryMangement/Templates/BulkUploadTemplate.xlsx
+++ b/LibraryMangement/Templates/BulkUploadTemplate.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sivaprasad\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Siva\LibraryMangement\LibraryMangement\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,47 +19,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>Sl.No</t>
-  </si>
-  <si>
-    <t>Acc. No</t>
-  </si>
-  <si>
-    <t>Call No</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Author</t>
   </si>
   <si>
-    <t>Publisher</t>
-  </si>
-  <si>
     <t>Place of Publishers</t>
   </si>
   <si>
-    <t>Year Published</t>
-  </si>
-  <si>
     <t>ISBN</t>
   </si>
   <si>
-    <t>Library Resource Type</t>
-  </si>
-  <si>
-    <t>Total Quantity</t>
-  </si>
-  <si>
     <t>Edition</t>
   </si>
   <si>
-    <t>Pages</t>
-  </si>
-  <si>
     <t>Vol.</t>
   </si>
   <si>
@@ -67,13 +40,37 @@
   </si>
   <si>
     <t>Price</t>
+  </si>
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t>Library Acc.No</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>Bill No. and Date</t>
+  </si>
+  <si>
+    <t>Title of the Book</t>
+  </si>
+  <si>
+    <t>LIBRARY BOOKS</t>
+  </si>
+  <si>
+    <t>University Details</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,6 +84,14 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,9 +114,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,78 +426,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="7" customWidth="1"/>
-    <col min="14" max="14" width="6" customWidth="1"/>
-    <col min="15" max="15" width="8" customWidth="1"/>
-    <col min="16" max="16" width="7" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="8.5703125" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" customWidth="1"/>
+    <col min="13" max="13" width="19.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="M3" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"-,Bold"University Details</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>